--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/105.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/105.xlsx
@@ -426,13 +426,13 @@
         <v>-7.618492584133782</v>
       </c>
       <c r="E2">
-        <v>-15.06473617533034</v>
+        <v>-16.62476830012874</v>
       </c>
       <c r="F2">
-        <v>-1.136752995128616</v>
+        <v>-1.974292910179321</v>
       </c>
       <c r="G2">
-        <v>-11.5171325041697</v>
+        <v>-9.180079167233643</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.617200770040101</v>
       </c>
       <c r="E3">
-        <v>-16.04866489382093</v>
+        <v>-16.03710369967935</v>
       </c>
       <c r="F3">
-        <v>-1.257834630028417</v>
+        <v>-1.536463461266656</v>
       </c>
       <c r="G3">
-        <v>-11.86903695397703</v>
+        <v>-8.670728582117921</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.57720433123658</v>
       </c>
       <c r="E4">
-        <v>-16.53368710241246</v>
+        <v>-16.25630448402063</v>
       </c>
       <c r="F4">
-        <v>-1.424093766342097</v>
+        <v>-1.657091979197125</v>
       </c>
       <c r="G4">
-        <v>-11.23976428330672</v>
+        <v>-8.415246109056435</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.526199595836028</v>
       </c>
       <c r="E5">
-        <v>-17.23323218169535</v>
+        <v>-16.96842513562282</v>
       </c>
       <c r="F5">
-        <v>-1.160921442472695</v>
+        <v>-1.394693350481937</v>
       </c>
       <c r="G5">
-        <v>-11.17070441314509</v>
+        <v>-8.716383498896034</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.50534363516963</v>
       </c>
       <c r="E6">
-        <v>-17.22997168040983</v>
+        <v>-18.22815150660255</v>
       </c>
       <c r="F6">
-        <v>-1.284702726738219</v>
+        <v>-1.89260428711965</v>
       </c>
       <c r="G6">
-        <v>-12.22816665365825</v>
+        <v>-9.042277705401643</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.539424602340547</v>
       </c>
       <c r="E7">
-        <v>-18.80237559619718</v>
+        <v>-17.94601399050267</v>
       </c>
       <c r="F7">
-        <v>-1.199462892622747</v>
+        <v>-1.411336908338985</v>
       </c>
       <c r="G7">
-        <v>-11.65315226269492</v>
+        <v>-7.878818883632175</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.647287297684196</v>
       </c>
       <c r="E8">
-        <v>-17.70355043518398</v>
+        <v>-17.7023186902539</v>
       </c>
       <c r="F8">
-        <v>-1.029151382974572</v>
+        <v>-1.737818867702146</v>
       </c>
       <c r="G8">
-        <v>-11.15622766362482</v>
+        <v>-8.754491606087425</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.840730919968215</v>
       </c>
       <c r="E9">
-        <v>-19.41533172397941</v>
+        <v>-20.1540164041106</v>
       </c>
       <c r="F9">
-        <v>-1.289121238464752</v>
+        <v>-1.743400407262209</v>
       </c>
       <c r="G9">
-        <v>-10.95929530807006</v>
+        <v>-9.913858744572265</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.109672407147729</v>
       </c>
       <c r="E10">
-        <v>-19.77443518431366</v>
+        <v>-19.62565669926566</v>
       </c>
       <c r="F10">
-        <v>-1.155211505965198</v>
+        <v>-0.7786481101635843</v>
       </c>
       <c r="G10">
-        <v>-11.08838512666174</v>
+        <v>-9.181595091594106</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.436801266937765</v>
       </c>
       <c r="E11">
-        <v>-19.72437290415886</v>
+        <v>-19.56555479223586</v>
       </c>
       <c r="F11">
-        <v>-0.5570937929782313</v>
+        <v>-1.237576905192955</v>
       </c>
       <c r="G11">
-        <v>-11.22535972066076</v>
+        <v>-9.441733618048442</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.800374150405244</v>
       </c>
       <c r="E12">
-        <v>-20.90681180924969</v>
+        <v>-21.3215656866642</v>
       </c>
       <c r="F12">
-        <v>-0.7923045751661368</v>
+        <v>-0.4537367353961314</v>
       </c>
       <c r="G12">
-        <v>-10.13574150886503</v>
+        <v>-8.534324920670244</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.16398925119104</v>
       </c>
       <c r="E13">
-        <v>-21.57043250422973</v>
+        <v>-22.10614645086313</v>
       </c>
       <c r="F13">
-        <v>-0.4059871531965594</v>
+        <v>-0.9594956248079667</v>
       </c>
       <c r="G13">
-        <v>-10.96661571336919</v>
+        <v>-9.171341274220842</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.495509591860086</v>
       </c>
       <c r="E14">
-        <v>-23.08380323285309</v>
+        <v>-22.04374860751144</v>
       </c>
       <c r="F14">
-        <v>-0.3774382990264773</v>
+        <v>-0.4082601933498413</v>
       </c>
       <c r="G14">
-        <v>-10.31468292660935</v>
+        <v>-9.153583303141126</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.764567610472515</v>
       </c>
       <c r="E15">
-        <v>-22.8638914780926</v>
+        <v>-24.47098803325271</v>
       </c>
       <c r="F15">
-        <v>0.1757785872591446</v>
+        <v>-0.1366418354414946</v>
       </c>
       <c r="G15">
-        <v>-10.85630104454065</v>
+        <v>-9.228467341570774</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.936573522226997</v>
       </c>
       <c r="E16">
-        <v>-23.7456306521261</v>
+        <v>-23.10539499692166</v>
       </c>
       <c r="F16">
-        <v>0.435085748827085</v>
+        <v>-0.1211770443986306</v>
       </c>
       <c r="G16">
-        <v>-10.30841907465237</v>
+        <v>-8.862342077524813</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.98980761375622</v>
       </c>
       <c r="E17">
-        <v>-24.81464034027279</v>
+        <v>-22.32056969512632</v>
       </c>
       <c r="F17">
-        <v>0.3230805355597582</v>
+        <v>1.469401855310604</v>
       </c>
       <c r="G17">
-        <v>-10.42179840441742</v>
+        <v>-8.404595263874478</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.907842085504599</v>
       </c>
       <c r="E18">
-        <v>-25.64813315222857</v>
+        <v>-24.7639350168089</v>
       </c>
       <c r="F18">
-        <v>1.23171508295573</v>
+        <v>0.8283001577923711</v>
       </c>
       <c r="G18">
-        <v>-9.370737827166737</v>
+        <v>-7.450655563561794</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.677195265757948</v>
       </c>
       <c r="E19">
-        <v>-25.9485430609494</v>
+        <v>-26.2551886783788</v>
       </c>
       <c r="F19">
-        <v>1.093304830356767</v>
+        <v>0.7544280095455168</v>
       </c>
       <c r="G19">
-        <v>-9.003329605491034</v>
+        <v>-8.124497066674039</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.301876608219878</v>
       </c>
       <c r="E20">
-        <v>-27.1095351131399</v>
+        <v>-25.48014488044003</v>
       </c>
       <c r="F20">
-        <v>1.733226932693413</v>
+        <v>1.159560968702282</v>
       </c>
       <c r="G20">
-        <v>-8.898261609936055</v>
+        <v>-6.687390929290002</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.790961356238661</v>
       </c>
       <c r="E21">
-        <v>-27.73301541451595</v>
+        <v>-27.50425955001849</v>
       </c>
       <c r="F21">
-        <v>1.736646433332169</v>
+        <v>1.911403790831169</v>
       </c>
       <c r="G21">
-        <v>-10.0747403188534</v>
+        <v>-7.037664611982285</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.159156157708033</v>
       </c>
       <c r="E22">
-        <v>-28.43706179696247</v>
+        <v>-28.04844627152023</v>
       </c>
       <c r="F22">
-        <v>1.910969726312103</v>
+        <v>1.300698206791262</v>
       </c>
       <c r="G22">
-        <v>-8.302093183578984</v>
+        <v>-6.109256096623641</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.439176045286618</v>
       </c>
       <c r="E23">
-        <v>-28.51157783675869</v>
+        <v>-29.35400079945759</v>
       </c>
       <c r="F23">
-        <v>2.020446762266085</v>
+        <v>1.92628458285506</v>
       </c>
       <c r="G23">
-        <v>-8.476431047475401</v>
+        <v>-7.364815526345161</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.663184148784286</v>
       </c>
       <c r="E24">
-        <v>-29.53371329045198</v>
+        <v>-28.52147708093946</v>
       </c>
       <c r="F24">
-        <v>2.347123387968904</v>
+        <v>2.465347983696449</v>
       </c>
       <c r="G24">
-        <v>-8.554773493428703</v>
+        <v>-5.821555309069969</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.863336553814276</v>
       </c>
       <c r="E25">
-        <v>-28.52405831112383</v>
+        <v>-30.72419476538043</v>
       </c>
       <c r="F25">
-        <v>2.140435780561594</v>
+        <v>2.244629489220521</v>
       </c>
       <c r="G25">
-        <v>-8.343600636305961</v>
+        <v>-5.51823590689334</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.079888361754322</v>
       </c>
       <c r="E26">
-        <v>-30.45536417015208</v>
+        <v>-30.86812099052921</v>
       </c>
       <c r="F26">
-        <v>1.982144710295442</v>
+        <v>3.046784033925839</v>
       </c>
       <c r="G26">
-        <v>-7.684166977061237</v>
+        <v>-5.849439129882129</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.338979441579936</v>
       </c>
       <c r="E27">
-        <v>-30.10773812719027</v>
+        <v>-29.51902744924511</v>
       </c>
       <c r="F27">
-        <v>2.195280329566143</v>
+        <v>2.46602890170155</v>
       </c>
       <c r="G27">
-        <v>-7.962217692008582</v>
+        <v>-5.924605353365889</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.658293346054681</v>
       </c>
       <c r="E28">
-        <v>-29.51482502536599</v>
+        <v>-31.20252615362563</v>
       </c>
       <c r="F28">
-        <v>1.979356425617619</v>
+        <v>2.306546639110173</v>
       </c>
       <c r="G28">
-        <v>-8.382036865653296</v>
+        <v>-5.636658474195259</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.05724540946843</v>
       </c>
       <c r="E29">
-        <v>-29.95232542772103</v>
+        <v>-29.21196521220701</v>
       </c>
       <c r="F29">
-        <v>2.016086236257749</v>
+        <v>2.401598485111805</v>
       </c>
       <c r="G29">
-        <v>-7.177172309025196</v>
+        <v>-5.717399493108515</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.537940706745049</v>
       </c>
       <c r="E30">
-        <v>-28.61037102571002</v>
+        <v>-29.42057389584435</v>
       </c>
       <c r="F30">
-        <v>1.671422440770542</v>
+        <v>2.267321785852811</v>
       </c>
       <c r="G30">
-        <v>-7.440345965422019</v>
+        <v>-5.445179508872303</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.095653563622528</v>
       </c>
       <c r="E31">
-        <v>-29.54714474435874</v>
+        <v>-29.03135155488508</v>
       </c>
       <c r="F31">
-        <v>1.833388148835512</v>
+        <v>2.207646198155134</v>
       </c>
       <c r="G31">
-        <v>-7.291837877641551</v>
+        <v>-5.754080268921547</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.728587518303938</v>
       </c>
       <c r="E32">
-        <v>-29.24653105430755</v>
+        <v>-29.28911229540168</v>
       </c>
       <c r="F32">
-        <v>1.572884824737929</v>
+        <v>1.788093019250435</v>
       </c>
       <c r="G32">
-        <v>-6.94510135179035</v>
+        <v>-5.162029775621581</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.423288452978323</v>
       </c>
       <c r="E33">
-        <v>-28.35117023045899</v>
+        <v>-27.99869192759796</v>
       </c>
       <c r="F33">
-        <v>1.878772742100091</v>
+        <v>1.644265243837163</v>
       </c>
       <c r="G33">
-        <v>-7.473801300442117</v>
+        <v>-5.589047949367716</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.167170557428946</v>
       </c>
       <c r="E34">
-        <v>-28.59078084715284</v>
+        <v>-27.0342628181844</v>
       </c>
       <c r="F34">
-        <v>1.426750874475263</v>
+        <v>1.372197910796499</v>
       </c>
       <c r="G34">
-        <v>-7.06463953442248</v>
+        <v>-6.237876700532314</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9551389545926297</v>
       </c>
       <c r="E35">
-        <v>-27.14963022200381</v>
+        <v>-27.04438848606555</v>
       </c>
       <c r="F35">
-        <v>1.730094047176025</v>
+        <v>1.649240418458376</v>
       </c>
       <c r="G35">
-        <v>-7.477801109523081</v>
+        <v>-5.904081312511562</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.7784699488878998</v>
       </c>
       <c r="E36">
-        <v>-26.52599595251149</v>
+        <v>-26.08514447939078</v>
       </c>
       <c r="F36">
-        <v>1.388314626985366</v>
+        <v>1.460317978371504</v>
       </c>
       <c r="G36">
-        <v>-7.232378861762854</v>
+        <v>-5.5650359699957</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6326013297349179</v>
       </c>
       <c r="E37">
-        <v>-27.43966992524708</v>
+        <v>-28.27685797199312</v>
       </c>
       <c r="F37">
-        <v>1.105468577299475</v>
+        <v>1.639561773724067</v>
       </c>
       <c r="G37">
-        <v>-6.649604381811437</v>
+        <v>-4.996689021241162</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.5187429328756955</v>
       </c>
       <c r="E38">
-        <v>-26.11162246691363</v>
+        <v>-24.95103797738382</v>
       </c>
       <c r="F38">
-        <v>1.09643937260896</v>
+        <v>1.109178006529211</v>
       </c>
       <c r="G38">
-        <v>-6.7474405650494</v>
+        <v>-4.509798397699838</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.4370345656196346</v>
       </c>
       <c r="E39">
-        <v>-25.53288801720736</v>
+        <v>-26.20113228414924</v>
       </c>
       <c r="F39">
-        <v>1.223172958298062</v>
+        <v>1.412564254334918</v>
       </c>
       <c r="G39">
-        <v>-6.707344037592986</v>
+        <v>-6.658785239734764</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.3896623366120253</v>
       </c>
       <c r="E40">
-        <v>-25.75927096132481</v>
+        <v>-25.73418321532232</v>
       </c>
       <c r="F40">
-        <v>0.9120596993590403</v>
+        <v>1.420718703048077</v>
       </c>
       <c r="G40">
-        <v>-6.883063295765928</v>
+        <v>-5.677181560454401</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3811126163517385</v>
       </c>
       <c r="E41">
-        <v>-26.15189418626384</v>
+        <v>-24.48661126857917</v>
       </c>
       <c r="F41">
-        <v>1.205460806491403</v>
+        <v>1.042128292211813</v>
       </c>
       <c r="G41">
-        <v>-7.101467965205687</v>
+        <v>-6.176983790832139</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.415580260275814</v>
       </c>
       <c r="E42">
-        <v>-25.45790101611435</v>
+        <v>-24.08335971514414</v>
       </c>
       <c r="F42">
-        <v>1.150816722398331</v>
+        <v>1.244975588339745</v>
       </c>
       <c r="G42">
-        <v>-7.162836652031982</v>
+        <v>-4.757458438563607</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4955617816442638</v>
       </c>
       <c r="E43">
-        <v>-23.62788127097865</v>
+        <v>-24.69596715042778</v>
       </c>
       <c r="F43">
-        <v>0.8642148549081464</v>
+        <v>1.184793039791555</v>
       </c>
       <c r="G43">
-        <v>-7.185132552528409</v>
+        <v>-5.608180752280838</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.622631371614604</v>
       </c>
       <c r="E44">
-        <v>-23.85440006931633</v>
+        <v>-23.60738539761994</v>
       </c>
       <c r="F44">
-        <v>1.15493536512505</v>
+        <v>1.076951201090699</v>
       </c>
       <c r="G44">
-        <v>-7.244942659113967</v>
+        <v>-6.532815862846121</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7978389271774273</v>
       </c>
       <c r="E45">
-        <v>-22.86765916846698</v>
+        <v>-23.07024045320011</v>
       </c>
       <c r="F45">
-        <v>0.66792325840597</v>
+        <v>1.08705065646563</v>
       </c>
       <c r="G45">
-        <v>-6.991760322365653</v>
+        <v>-5.760629587154199</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.018073303536224</v>
       </c>
       <c r="E46">
-        <v>-22.377651109993</v>
+        <v>-21.42484659335714</v>
       </c>
       <c r="F46">
-        <v>0.9175285809523227</v>
+        <v>1.548085161432917</v>
       </c>
       <c r="G46">
-        <v>-7.084133271707141</v>
+        <v>-5.994534747240775</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.279030977917575</v>
       </c>
       <c r="E47">
-        <v>-22.21826241034503</v>
+        <v>-21.3594101439463</v>
       </c>
       <c r="F47">
-        <v>0.6288234886264306</v>
+        <v>1.417116961580704</v>
       </c>
       <c r="G47">
-        <v>-5.987785274492997</v>
+        <v>-5.326084291150697</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.577413013118673</v>
       </c>
       <c r="E48">
-        <v>-21.56168349244691</v>
+        <v>-21.23479106772922</v>
       </c>
       <c r="F48">
-        <v>1.158543733531644</v>
+        <v>1.546486412345514</v>
       </c>
       <c r="G48">
-        <v>-6.633815143667389</v>
+        <v>-4.950830668726362</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.905449874065886</v>
       </c>
       <c r="E49">
-        <v>-21.77890533364684</v>
+        <v>-20.84272031661913</v>
       </c>
       <c r="F49">
-        <v>1.034152770857659</v>
+        <v>1.08865437575745</v>
       </c>
       <c r="G49">
-        <v>-6.441935869314181</v>
+        <v>-5.395580563779736</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.255274838124693</v>
       </c>
       <c r="E50">
-        <v>-20.43574635754979</v>
+        <v>-19.3698658449424</v>
       </c>
       <c r="F50">
-        <v>0.8199452441677353</v>
+        <v>1.427590839021701</v>
       </c>
       <c r="G50">
-        <v>-7.052836980473158</v>
+        <v>-7.087102777218439</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.621947467871351</v>
       </c>
       <c r="E51">
-        <v>-19.90913011519781</v>
+        <v>-18.80499758264762</v>
       </c>
       <c r="F51">
-        <v>1.101573593771511</v>
+        <v>1.265870327707959</v>
       </c>
       <c r="G51">
-        <v>-7.384653791893564</v>
+        <v>-4.526496534215853</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.995938644019299</v>
       </c>
       <c r="E52">
-        <v>-19.98173513896279</v>
+        <v>-19.16790496114832</v>
       </c>
       <c r="F52">
-        <v>1.217357819130409</v>
+        <v>0.8482654689346448</v>
       </c>
       <c r="G52">
-        <v>-7.368513463042655</v>
+        <v>-5.483477926914142</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.369320981939351</v>
       </c>
       <c r="E53">
-        <v>-18.62702402567217</v>
+        <v>-19.32463997502779</v>
       </c>
       <c r="F53">
-        <v>0.8604822313911319</v>
+        <v>1.52336667813338</v>
       </c>
       <c r="G53">
-        <v>-6.760965760317431</v>
+        <v>-5.870291292892401</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.738009083924937</v>
       </c>
       <c r="E54">
-        <v>-19.15838158031018</v>
+        <v>-16.87786471241743</v>
       </c>
       <c r="F54">
-        <v>0.8677171922871828</v>
+        <v>0.9785776018038406</v>
       </c>
       <c r="G54">
-        <v>-7.245815464048779</v>
+        <v>-5.401083172334926</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.093380041107156</v>
       </c>
       <c r="E55">
-        <v>-17.7056244762795</v>
+        <v>-17.65736452877975</v>
       </c>
       <c r="F55">
-        <v>0.4095761746578742</v>
+        <v>1.046362906374924</v>
       </c>
       <c r="G55">
-        <v>-7.570636711104449</v>
+        <v>-5.63818752344196</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.428838972091333</v>
       </c>
       <c r="E56">
-        <v>-17.50767582045621</v>
+        <v>-16.97013689879772</v>
       </c>
       <c r="F56">
-        <v>0.6870353511233602</v>
+        <v>1.058574698626994</v>
       </c>
       <c r="G56">
-        <v>-7.774997752269785</v>
+        <v>-4.733741769131941</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.740556435157238</v>
       </c>
       <c r="E57">
-        <v>-16.89942930564196</v>
+        <v>-18.68420959544103</v>
       </c>
       <c r="F57">
-        <v>0.7043482298418698</v>
+        <v>0.6964787395152746</v>
       </c>
       <c r="G57">
-        <v>-7.957489451741422</v>
+        <v>-5.385549869472514</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.021031928683758</v>
       </c>
       <c r="E58">
-        <v>-16.83631143492305</v>
+        <v>-16.08626934198062</v>
       </c>
       <c r="F58">
-        <v>0.6725248393285213</v>
+        <v>1.014091369096661</v>
       </c>
       <c r="G58">
-        <v>-7.23582742562183</v>
+        <v>-6.822065386975851</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.266722187769853</v>
       </c>
       <c r="E59">
-        <v>-16.42552902921326</v>
+        <v>-15.35482116331369</v>
       </c>
       <c r="F59">
-        <v>0.5897833612998926</v>
+        <v>1.43718333354612</v>
       </c>
       <c r="G59">
-        <v>-7.504959780370604</v>
+        <v>-6.420109183500754</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.476492034575532</v>
       </c>
       <c r="E60">
-        <v>-15.33847790062001</v>
+        <v>-15.44696655242177</v>
       </c>
       <c r="F60">
-        <v>0.3796911638670765</v>
+        <v>0.7944994542885401</v>
       </c>
       <c r="G60">
-        <v>-7.268354174940606</v>
+        <v>-5.882362907009598</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.646429210316945</v>
       </c>
       <c r="E61">
-        <v>-15.3525252269918</v>
+        <v>-14.87878344715337</v>
       </c>
       <c r="F61">
-        <v>-0.1432381250699871</v>
+        <v>0.7338347959119211</v>
       </c>
       <c r="G61">
-        <v>-7.785661722337981</v>
+        <v>-5.621755165872261</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.776267272074747</v>
       </c>
       <c r="E62">
-        <v>-15.06868047619102</v>
+        <v>-14.58329146120487</v>
       </c>
       <c r="F62">
-        <v>0.4335101940269603</v>
+        <v>0.9302241397676279</v>
       </c>
       <c r="G62">
-        <v>-8.017975489968226</v>
+        <v>-5.999374549040956</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.865767488055496</v>
       </c>
       <c r="E63">
-        <v>-14.43694476669899</v>
+        <v>-12.28633623266427</v>
       </c>
       <c r="F63">
-        <v>0.4300393346092304</v>
+        <v>0.6488418152824834</v>
       </c>
       <c r="G63">
-        <v>-7.827467766226866</v>
+        <v>-7.300995767013961</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.912556247721611</v>
       </c>
       <c r="E64">
-        <v>-14.74684182846589</v>
+        <v>-13.3845908059525</v>
       </c>
       <c r="F64">
-        <v>-0.2823839679226368</v>
+        <v>0.9068575520694594</v>
       </c>
       <c r="G64">
-        <v>-7.759838508665151</v>
+        <v>-7.353295157449951</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.917589252066377</v>
       </c>
       <c r="E65">
-        <v>-14.19706697003868</v>
+        <v>-12.59751032410134</v>
       </c>
       <c r="F65">
-        <v>-0.2934302472389682</v>
+        <v>0.3079048447404713</v>
       </c>
       <c r="G65">
-        <v>-8.04566571870838</v>
+        <v>-7.686470394595967</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.879968322330472</v>
       </c>
       <c r="E66">
-        <v>-14.41685645600096</v>
+        <v>-13.0389776696871</v>
       </c>
       <c r="F66">
-        <v>0.06035801519007542</v>
+        <v>0.5723387721643378</v>
       </c>
       <c r="G66">
-        <v>-8.103037877675272</v>
+        <v>-6.293424500312153</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.799103230595296</v>
       </c>
       <c r="E67">
-        <v>-14.30182415925812</v>
+        <v>-13.35189522361712</v>
       </c>
       <c r="F67">
-        <v>-0.2060482550198568</v>
+        <v>0.4171896994570045</v>
       </c>
       <c r="G67">
-        <v>-8.51159589892797</v>
+        <v>-8.301000536799689</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.677270493094476</v>
       </c>
       <c r="E68">
-        <v>-13.17614514737943</v>
+        <v>-12.6332626263919</v>
       </c>
       <c r="F68">
-        <v>-0.2617501642863039</v>
+        <v>0.2190541571161963</v>
       </c>
       <c r="G68">
-        <v>-8.453032656535001</v>
+        <v>-7.15227111861057</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.51419650347683</v>
       </c>
       <c r="E69">
-        <v>-12.70610313080527</v>
+        <v>-12.05323756159345</v>
       </c>
       <c r="F69">
-        <v>-0.7807720441843622</v>
+        <v>0.465924210498505</v>
       </c>
       <c r="G69">
-        <v>-7.715712641133738</v>
+        <v>-7.155883743547519</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.312486062141578</v>
       </c>
       <c r="E70">
-        <v>-13.98254862782133</v>
+        <v>-12.75648240414061</v>
       </c>
       <c r="F70">
-        <v>-0.5354526945800941</v>
+        <v>0.05028755267424184</v>
       </c>
       <c r="G70">
-        <v>-7.629659324515742</v>
+        <v>-6.603867434494337</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.077422237061563</v>
       </c>
       <c r="E71">
-        <v>-13.67479806273406</v>
+        <v>-13.11065435628051</v>
       </c>
       <c r="F71">
-        <v>-0.9786955244700537</v>
+        <v>-0.3764575120215627</v>
       </c>
       <c r="G71">
-        <v>-7.265502793405448</v>
+        <v>-7.197109011220382</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.811077028970661</v>
       </c>
       <c r="E72">
-        <v>-13.28907623218272</v>
+        <v>-13.95357545112025</v>
       </c>
       <c r="F72">
-        <v>-0.8672212947079214</v>
+        <v>-0.6292064888615394</v>
       </c>
       <c r="G72">
-        <v>-7.038767102426259</v>
+        <v>-7.450754000208578</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.519324987918218</v>
       </c>
       <c r="E73">
-        <v>-14.16852399836833</v>
+        <v>-12.98697720265702</v>
       </c>
       <c r="F73">
-        <v>-1.218052285508971</v>
+        <v>-0.9233986868635754</v>
       </c>
       <c r="G73">
-        <v>-6.993174528857774</v>
+        <v>-7.091535707545249</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.207856263152387</v>
       </c>
       <c r="E74">
-        <v>-13.38467231848464</v>
+        <v>-12.95780930157362</v>
       </c>
       <c r="F74">
-        <v>-0.7792751842875034</v>
+        <v>-0.8583039196167846</v>
       </c>
       <c r="G74">
-        <v>-5.990866341537315</v>
+        <v>-6.893363050241025</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.877795267496651</v>
       </c>
       <c r="E75">
-        <v>-13.19089891569642</v>
+        <v>-13.63454898575388</v>
       </c>
       <c r="F75">
-        <v>-1.230825710860139</v>
+        <v>-0.575992995273102</v>
       </c>
       <c r="G75">
-        <v>-6.657531813099055</v>
+        <v>-6.473806374321067</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.535638729281542</v>
       </c>
       <c r="E76">
-        <v>-14.29709643239411</v>
+        <v>-13.26029777986397</v>
       </c>
       <c r="F76">
-        <v>-1.51495573002037</v>
+        <v>-1.416756916255502</v>
       </c>
       <c r="G76">
-        <v>-6.341084243463088</v>
+        <v>-5.659039686452231</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.186953122503363</v>
       </c>
       <c r="E77">
-        <v>-14.87660525115568</v>
+        <v>-13.19793616430434</v>
       </c>
       <c r="F77">
-        <v>-1.245003218959053</v>
+        <v>-1.189213502747909</v>
       </c>
       <c r="G77">
-        <v>-6.654322778413919</v>
+        <v>-5.605975771392891</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.833719505761935</v>
       </c>
       <c r="E78">
-        <v>-14.3617403988536</v>
+        <v>-13.8964532799875</v>
       </c>
       <c r="F78">
-        <v>-1.353944301203424</v>
+        <v>-1.119177523943419</v>
       </c>
       <c r="G78">
-        <v>-6.042414332236192</v>
+        <v>-5.202014741544974</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.483745956803706</v>
       </c>
       <c r="E79">
-        <v>-14.97897593457308</v>
+        <v>-15.14535206961489</v>
       </c>
       <c r="F79">
-        <v>-1.80428458300057</v>
+        <v>-1.466645343089102</v>
       </c>
       <c r="G79">
-        <v>-5.406592343333233</v>
+        <v>-5.088789629193215</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.142627393250818</v>
       </c>
       <c r="E80">
-        <v>-15.448873039979</v>
+        <v>-15.55344909023813</v>
       </c>
       <c r="F80">
-        <v>-1.311187289340525</v>
+        <v>-1.395389179100289</v>
       </c>
       <c r="G80">
-        <v>-4.827292677013268</v>
+        <v>-5.661333260322283</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.811726971443111</v>
       </c>
       <c r="E81">
-        <v>-15.82496280631602</v>
+        <v>-14.81412136679785</v>
       </c>
       <c r="F81">
-        <v>-1.85008087486434</v>
+        <v>-1.182417576575342</v>
       </c>
       <c r="G81">
-        <v>-4.453394199092983</v>
+        <v>-3.915388706098631</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.497741126701613</v>
       </c>
       <c r="E82">
-        <v>-15.89094720108178</v>
+        <v>-15.54864890779</v>
       </c>
       <c r="F82">
-        <v>-2.048996739298586</v>
+        <v>-2.34602609565521</v>
       </c>
       <c r="G82">
-        <v>-5.170475639915591</v>
+        <v>-3.384057217756189</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.20394996137071</v>
       </c>
       <c r="E83">
-        <v>-17.11083658621604</v>
+        <v>-17.43466776250455</v>
       </c>
       <c r="F83">
-        <v>-1.752249856226316</v>
+        <v>-1.503781053756604</v>
       </c>
       <c r="G83">
-        <v>-5.263120930646513</v>
+        <v>-4.002193422453741</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.9297607172143977</v>
       </c>
       <c r="E84">
-        <v>-18.33346569812494</v>
+        <v>-18.22990402604352</v>
       </c>
       <c r="F84">
-        <v>-1.927608608459749</v>
+        <v>-1.02519178678919</v>
       </c>
       <c r="G84">
-        <v>-3.759360058503916</v>
+        <v>-3.48580461709301</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.679297649933257</v>
       </c>
       <c r="E85">
-        <v>-18.69999585583177</v>
+        <v>-17.90944203441672</v>
       </c>
       <c r="F85">
-        <v>-1.662826766726706</v>
+        <v>-1.479853661326741</v>
       </c>
       <c r="G85">
-        <v>-4.199900146296523</v>
+        <v>-1.851546282309737</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4531806776026799</v>
       </c>
       <c r="E86">
-        <v>-19.33784953370817</v>
+        <v>-19.04847098767002</v>
       </c>
       <c r="F86">
-        <v>-2.368452486351201</v>
+        <v>-1.77883465128436</v>
       </c>
       <c r="G86">
-        <v>-3.774929454803481</v>
+        <v>-2.928964912347444</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2495320961885713</v>
       </c>
       <c r="E87">
-        <v>-21.2884444277721</v>
+        <v>-21.32891539997865</v>
       </c>
       <c r="F87">
-        <v>-2.259812101474046</v>
+        <v>-2.236742897673482</v>
       </c>
       <c r="G87">
-        <v>-4.235583430755484</v>
+        <v>-4.505473747684491</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.0709661702110846</v>
       </c>
       <c r="E88">
-        <v>-21.21097582292288</v>
+        <v>-22.59511748878935</v>
       </c>
       <c r="F88">
-        <v>-2.437569805705986</v>
+        <v>-2.689567453311624</v>
       </c>
       <c r="G88">
-        <v>-3.937408983984064</v>
+        <v>-4.231921587495144</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.08183977691716393</v>
       </c>
       <c r="E89">
-        <v>-22.34401360506403</v>
+        <v>-22.64829083058741</v>
       </c>
       <c r="F89">
-        <v>-2.43726910833877</v>
+        <v>-1.855518278496316</v>
       </c>
       <c r="G89">
-        <v>-3.747711721967887</v>
+        <v>-3.120237160712155</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.2086271376891098</v>
       </c>
       <c r="E90">
-        <v>-24.45281526705993</v>
+        <v>-25.02074024930988</v>
       </c>
       <c r="F90">
-        <v>-3.045576568747573</v>
+        <v>-1.977241069765884</v>
       </c>
       <c r="G90">
-        <v>-4.00792571651809</v>
+        <v>-2.800856179002044</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.3060464536112535</v>
       </c>
       <c r="E91">
-        <v>-25.91708375201812</v>
+        <v>-25.08709145047027</v>
       </c>
       <c r="F91">
-        <v>-2.905839271569324</v>
+        <v>-2.547625042107123</v>
       </c>
       <c r="G91">
-        <v>-3.897955575953301</v>
+        <v>-2.227961457166116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.3724417273494939</v>
       </c>
       <c r="E92">
-        <v>-27.65042510556406</v>
+        <v>-28.78588562129931</v>
       </c>
       <c r="F92">
-        <v>-3.090112913791685</v>
+        <v>-2.99868766027951</v>
       </c>
       <c r="G92">
-        <v>-4.136910536019863</v>
+        <v>-1.606865590621944</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.4075474246848408</v>
       </c>
       <c r="E93">
-        <v>-28.6710480489388</v>
+        <v>-29.45684017993478</v>
       </c>
       <c r="F93">
-        <v>-3.160365096488306</v>
+        <v>-2.967712517986628</v>
       </c>
       <c r="G93">
-        <v>-3.751731218378207</v>
+        <v>-2.597925750436626</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.4101918229905412</v>
       </c>
       <c r="E94">
-        <v>-29.77792483673763</v>
+        <v>-30.78647033993391</v>
       </c>
       <c r="F94">
-        <v>-3.382326142068433</v>
+        <v>-4.04945017317821</v>
       </c>
       <c r="G94">
-        <v>-4.584321501757946</v>
+        <v>-3.562155361559729</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.3814201031392936</v>
       </c>
       <c r="E95">
-        <v>-32.50296803440833</v>
+        <v>-32.61283107807142</v>
       </c>
       <c r="F95">
-        <v>-3.74773225732174</v>
+        <v>-3.588359339227532</v>
       </c>
       <c r="G95">
-        <v>-4.361001562422139</v>
+        <v>-4.40992457587346</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3221663978254962</v>
       </c>
       <c r="E96">
-        <v>-33.93300578434253</v>
+        <v>-34.01409037568688</v>
       </c>
       <c r="F96">
-        <v>-3.564369819242458</v>
+        <v>-3.307983481136789</v>
       </c>
       <c r="G96">
-        <v>-4.735067382641956</v>
+        <v>-3.912803103509789</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.2380423906753762</v>
       </c>
       <c r="E97">
-        <v>-35.83348632080058</v>
+        <v>-36.49344574454543</v>
       </c>
       <c r="F97">
-        <v>-3.791735962125853</v>
+        <v>-3.713263889691253</v>
       </c>
       <c r="G97">
-        <v>-4.874604610678902</v>
+        <v>-4.391119895116282</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.1291306003883818</v>
       </c>
       <c r="E98">
-        <v>-38.5957399893923</v>
+        <v>-37.63744922649614</v>
       </c>
       <c r="F98">
-        <v>-3.71131888302948</v>
+        <v>-4.002064244268467</v>
       </c>
       <c r="G98">
-        <v>-6.332848377348882</v>
+        <v>-4.517414112939309</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.007721901064966421</v>
       </c>
       <c r="E99">
-        <v>-40.64917426393342</v>
+        <v>-39.88657471256773</v>
       </c>
       <c r="F99">
-        <v>-3.648235391836686</v>
+        <v>-4.484043190648137</v>
       </c>
       <c r="G99">
-        <v>-5.925986747642416</v>
+        <v>-5.000062117004271</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.1320089160307467</v>
       </c>
       <c r="E100">
-        <v>-41.57639743089996</v>
+        <v>-42.11188268959597</v>
       </c>
       <c r="F100">
-        <v>-4.053570472639734</v>
+        <v>-4.377224385689738</v>
       </c>
       <c r="G100">
-        <v>-6.343528753524875</v>
+        <v>-5.814818961208428</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.267563122366666</v>
       </c>
       <c r="E101">
-        <v>-44.3698364357455</v>
+        <v>-44.5060936901623</v>
       </c>
       <c r="F101">
-        <v>-4.182316162750237</v>
+        <v>-4.350186473662362</v>
       </c>
       <c r="G101">
-        <v>-6.438598866988226</v>
+        <v>-5.497692178709656</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.4246579180168732</v>
       </c>
       <c r="E102">
-        <v>-45.60087265964964</v>
+        <v>-46.2870542121359</v>
       </c>
       <c r="F102">
-        <v>-3.97198705224022</v>
+        <v>-4.317152838373524</v>
       </c>
       <c r="G102">
-        <v>-7.058615211639339</v>
+        <v>-5.944765178627118</v>
       </c>
     </row>
   </sheetData>
